--- a/002/xy_002_data.xlsx
+++ b/002/xy_002_data.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>

--- a/002/xy_002_data.xlsx
+++ b/002/xy_002_data.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Money growth matters for inflation, but only some of the time.</t>
+          <t>Money growth and inflation line up in some decades, not in months.</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2 money stock, % change year on year, monthly, FRED M2SL, shifted forward 18 months, 1960 - present</t>
+          <t>M2 money stock, % change year on year, monthly, FRED M2SL, shifted forward 18 months, 1960 - present (pairs from 07/1961)</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CPI all urban consumers, % change year on year, monthly, FRED CPIAUCSL, 1960 - present</t>
+          <t>CPI all urban consumers, % change year on year, monthly, FRED CPIAUCSL, 07/1961 - present</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>

--- a/002/xy_002_data.xlsx
+++ b/002/xy_002_data.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26/09/2026 19:05</t>
+          <t>26/09/2026 19:28</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26/09/2026 19:05</t>
+          <t>26/09/2026 19:28</t>
         </is>
       </c>
     </row>

--- a/002/xy_002_data.xlsx
+++ b/002/xy_002_data.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Position of each film in its franchise, in release order, films 1-10, 35 franchises, Wikipedia franchise pages</t>
+          <t>Position of each film in its franchise, in release order, films 1-10, 87 franchises, Wikipedia franchise pages (TV and shorts removed)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26/09/2026 19:28</t>
+          <t>26/09/2026 19:36</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26/09/2026 19:28</t>
+          <t>26/09/2026 19:36</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C223"/>
+  <dimension ref="A1:C422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -3663,27 +3663,2614 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>The Purge | The Purge: Season 1</t>
+          <t>The Purge | The Forever Purge</t>
         </is>
       </c>
       <c r="B222" t="n">
         <v>5</v>
       </c>
       <c r="C222" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>The Purge | The Forever Purge</t>
+          <t>Jurassic Park (franchise) | Jurassic Park</t>
         </is>
       </c>
       <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | The Lost World: Jurassic Park</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>2</v>
+      </c>
+      <c r="C224" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic Park III</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>3</v>
+      </c>
+      <c r="C225" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>4</v>
+      </c>
+      <c r="C226" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World: Fallen Kingdom</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>5</v>
+      </c>
+      <c r="C227" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World Dominion</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
         <v>6</v>
       </c>
-      <c r="C223" t="n">
+      <c r="C228" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World Rebirth</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>7</v>
+      </c>
+      <c r="C229" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Battle of the Smithsonian</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>2</v>
+      </c>
+      <c r="C231" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Secret of the Tomb</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>3</v>
+      </c>
+      <c r="C232" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Kahmunrah Rises Again</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>4</v>
+      </c>
+      <c r="C233" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Dr. No</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>List of James Bond films | From Russia with Love</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>2</v>
+      </c>
+      <c r="C235" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Goldfinger</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>3</v>
+      </c>
+      <c r="C236" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Thunderball</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>4</v>
+      </c>
+      <c r="C237" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>List of James Bond films | You Only Live Twice</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>5</v>
+      </c>
+      <c r="C238" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>List of James Bond films | On Her Majesty's Secret Service</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>6</v>
+      </c>
+      <c r="C239" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Diamonds Are Forever</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>7</v>
+      </c>
+      <c r="C240" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Live and Let Die</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>8</v>
+      </c>
+      <c r="C241" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>List of James Bond films | The Man with the Golden Gun</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>9</v>
+      </c>
+      <c r="C242" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>List of James Bond films | The Spy Who Loved Me</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>10</v>
+      </c>
+      <c r="C243" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 2: Their First Assignment</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>2</v>
+      </c>
+      <c r="C245" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 3: Back in Training</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>3</v>
+      </c>
+      <c r="C246" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 4: Citizens on Patrol</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>4</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 5: Assignment Miami Beach</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>5</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 6: City Under Siege</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>6</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy: Mission to Moscow</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>7</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 2</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2</v>
+      </c>
+      <c r="C252" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 3</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>3</v>
+      </c>
+      <c r="C253" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 4</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>4</v>
+      </c>
+      <c r="C254" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop II</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>2</v>
+      </c>
+      <c r="C256" t="n">
         <v>48</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop III</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>3</v>
+      </c>
+      <c r="C257" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop: Axel F</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>4</v>
+      </c>
+      <c r="C258" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future Part II</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>2</v>
+      </c>
+      <c r="C260" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future Part III</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>3</v>
+      </c>
+      <c r="C261" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid (1984)</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid Part II</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2</v>
+      </c>
+      <c r="C263" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid Part III</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>3</v>
+      </c>
+      <c r="C264" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Next Karate Kid</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>4</v>
+      </c>
+      <c r="C265" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid (2010)</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>5</v>
+      </c>
+      <c r="C266" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | Karate Kid: Legends</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>6</v>
+      </c>
+      <c r="C267" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>1</v>
+      </c>
+      <c r="C268" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone 2: Lost in New York</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>2</v>
+      </c>
+      <c r="C269" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone 3</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>3</v>
+      </c>
+      <c r="C270" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Sweet Home Alone</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>4</v>
+      </c>
+      <c r="C271" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
+      <c r="C272" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws 2</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>2</v>
+      </c>
+      <c r="C273" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws 3-D</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>3</v>
+      </c>
+      <c r="C274" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws: The Revenge</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>4</v>
+      </c>
+      <c r="C275" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play (1988)</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play 2</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>2</v>
+      </c>
+      <c r="C277" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play 3</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>3</v>
+      </c>
+      <c r="C278" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Bride of Chucky</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>4</v>
+      </c>
+      <c r="C279" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Seed of Chucky</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>5</v>
+      </c>
+      <c r="C280" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Curse of Chucky</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>6</v>
+      </c>
+      <c r="C281" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Cult of Chucky</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>7</v>
+      </c>
+      <c r="C282" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play (2019)</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>8</v>
+      </c>
+      <c r="C283" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>1</v>
+      </c>
+      <c r="C284" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Evolution</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>2</v>
+      </c>
+      <c r="C285" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Rise of the Lycans</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>3</v>
+      </c>
+      <c r="C286" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Awakening</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>4</v>
+      </c>
+      <c r="C287" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Blood Wars</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>5</v>
+      </c>
+      <c r="C288" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1</v>
+      </c>
+      <c r="C289" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade II</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>2</v>
+      </c>
+      <c r="C290" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade: Trinity</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>3</v>
+      </c>
+      <c r="C291" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon (2010)</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>1</v>
+      </c>
+      <c r="C292" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon 2</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2</v>
+      </c>
+      <c r="C293" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon: The Hidden World</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>3</v>
+      </c>
+      <c r="C294" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon (2025)</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>4</v>
+      </c>
+      <c r="C295" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>1</v>
+      </c>
+      <c r="C296" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania 2</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>2</v>
+      </c>
+      <c r="C297" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania 3: Summer Vacation</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>3</v>
+      </c>
+      <c r="C298" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania: Transformania</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>4</v>
+      </c>
+      <c r="C299" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Fellowship of the Ring</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>1</v>
+      </c>
+      <c r="C300" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Two Towers</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>2</v>
+      </c>
+      <c r="C301" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Return of the King</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>3</v>
+      </c>
+      <c r="C302" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Finding Nemo (franchise) | Finding Nemo</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>1</v>
+      </c>
+      <c r="C303" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Finding Nemo (franchise) | Finding Dory</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>2</v>
+      </c>
+      <c r="C304" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>The Incredibles (franchise) | The Incredibles</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>1</v>
+      </c>
+      <c r="C305" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>The Incredibles (franchise) | Incredibles 2</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>2</v>
+      </c>
+      <c r="C306" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Monsters, Inc. (franchise) | Monsters, Inc.</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>1</v>
+      </c>
+      <c r="C307" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Monsters, Inc. (franchise) | Monsters University</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>2</v>
+      </c>
+      <c r="C308" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Frozen (franchise) | Frozen</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Frozen (franchise) | Frozen 2</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>2</v>
+      </c>
+      <c r="C310" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>National Treasure (franchise) | National Treasure</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>National Treasure (franchise) | National Treasure: Book of Secrets</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>2</v>
+      </c>
+      <c r="C312" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>1</v>
+      </c>
+      <c r="C313" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect 2</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>2</v>
+      </c>
+      <c r="C314" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect 3</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>3</v>
+      </c>
+      <c r="C315" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>1</v>
+      </c>
+      <c r="C316" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys II</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>2</v>
+      </c>
+      <c r="C317" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys for Life</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>3</v>
+      </c>
+      <c r="C318" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys: Ride or Die</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>4</v>
+      </c>
+      <c r="C319" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>1</v>
+      </c>
+      <c r="C320" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour 2</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>2</v>
+      </c>
+      <c r="C321" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour 3</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>3</v>
+      </c>
+      <c r="C322" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Pie</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Pie 2</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>2</v>
+      </c>
+      <c r="C324" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Wedding</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>3</v>
+      </c>
+      <c r="C325" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Reunion</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>4</v>
+      </c>
+      <c r="C326" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie (2000)</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 2</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>2</v>
+      </c>
+      <c r="C328" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 3</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>3</v>
+      </c>
+      <c r="C329" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 4</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>4</v>
+      </c>
+      <c r="C330" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 5</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>5</v>
+      </c>
+      <c r="C331" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie (2026)</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>6</v>
+      </c>
+      <c r="C332" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>1</v>
+      </c>
+      <c r="C333" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables 2</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>2</v>
+      </c>
+      <c r="C334" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables 3</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>3</v>
+      </c>
+      <c r="C335" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | Expend4bles</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>4</v>
+      </c>
+      <c r="C336" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken (2008)</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>1</v>
+      </c>
+      <c r="C337" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken 2 (2012)</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>2</v>
+      </c>
+      <c r="C338" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken 3 (2014)</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>3</v>
+      </c>
+      <c r="C339" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | Kingsman: The Secret Service</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>1</v>
+      </c>
+      <c r="C340" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | Kingsman: The Golden Circle</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>2</v>
+      </c>
+      <c r="C341" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | The King's Man</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>3</v>
+      </c>
+      <c r="C342" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>1</v>
+      </c>
+      <c r="C343" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me 2</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>2</v>
+      </c>
+      <c r="C344" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me: Now You Don't</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>3</v>
+      </c>
+      <c r="C345" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Zombieland (film series) | Zombieland</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>1</v>
+      </c>
+      <c r="C346" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Zombieland (film series) | Zombieland: Double Tap</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>2</v>
+      </c>
+      <c r="C347" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>1</v>
+      </c>
+      <c r="C348" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy Returns</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>2</v>
+      </c>
+      <c r="C349" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy: Tomb of the Dragon Emperor</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>3</v>
+      </c>
+      <c r="C350" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>1</v>
+      </c>
+      <c r="C351" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Zathura: A Space Adventure</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>2</v>
+      </c>
+      <c r="C352" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji: Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>3</v>
+      </c>
+      <c r="C353" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji: The Next Level</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>4</v>
+      </c>
+      <c r="C354" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Top Gun (franchise) | Top Gun</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>1</v>
+      </c>
+      <c r="C355" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Top Gun (franchise) | Top Gun: Maverick</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>2</v>
+      </c>
+      <c r="C356" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1</v>
+      </c>
+      <c r="C357" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar: The Way of Water</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>2</v>
+      </c>
+      <c r="C358" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar: Fire and Ash</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>3</v>
+      </c>
+      <c r="C359" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>1</v>
+      </c>
+      <c r="C360" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron: Legacy</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>2</v>
+      </c>
+      <c r="C361" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron: Ares</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>3</v>
+      </c>
+      <c r="C362" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Legally Blonde (franchise) | Legally Blonde (2001)</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>1</v>
+      </c>
+      <c r="C363" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Legally Blonde (franchise) | Legally Blonde 2: Red, White &amp; Blonde (2003)</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>2</v>
+      </c>
+      <c r="C364" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>1</v>
+      </c>
+      <c r="C365" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause 2</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>2</v>
+      </c>
+      <c r="C366" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause 3: The Escape Clause</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>3</v>
+      </c>
+      <c r="C367" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clauses</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>4</v>
+      </c>
+      <c r="C368" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1</v>
+      </c>
+      <c r="C369" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog 2</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>2</v>
+      </c>
+      <c r="C370" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog 3</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>3</v>
+      </c>
+      <c r="C371" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Movie</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
+      <c r="C372" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Batman Movie</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>2</v>
+      </c>
+      <c r="C373" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Ninjago Movie</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>3</v>
+      </c>
+      <c r="C374" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Movie 2: The Second Part</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>4</v>
+      </c>
+      <c r="C375" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C376" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls World Tour</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>2</v>
+      </c>
+      <c r="C377" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls Band Together</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>3</v>
+      </c>
+      <c r="C378" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>1</v>
+      </c>
+      <c r="C379" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop 2</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>2</v>
+      </c>
+      <c r="C380" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop 3</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>3</v>
+      </c>
+      <c r="C381" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species II</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>2</v>
+      </c>
+      <c r="C383" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species III</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>3</v>
+      </c>
+      <c r="C384" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>1</v>
+      </c>
+      <c r="C385" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers 2</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>2</v>
+      </c>
+      <c r="C386" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers 3</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>3</v>
+      </c>
+      <c r="C387" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers: Reborn</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>4</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>1</v>
+      </c>
+      <c r="C389" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Exorcist II: The Heretic</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>2</v>
+      </c>
+      <c r="C390" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist III</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>3</v>
+      </c>
+      <c r="C391" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Exorcist: The Beginning</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>4</v>
+      </c>
+      <c r="C392" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Dominion: Prequel to the Exorcist</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>5</v>
+      </c>
+      <c r="C393" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist: Believer</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>6</v>
+      </c>
+      <c r="C394" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Omen (1976)</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>1</v>
+      </c>
+      <c r="C395" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | Damien – Omen II</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>2</v>
+      </c>
+      <c r="C396" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Final Conflict</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>3</v>
+      </c>
+      <c r="C397" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | Omen IV: The Awakening</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>4</v>
+      </c>
+      <c r="C398" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Omen (2006)</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>5</v>
+      </c>
+      <c r="C399" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The First Omen</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>6</v>
+      </c>
+      <c r="C400" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist (1982)</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>1</v>
+      </c>
+      <c r="C401" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist II: The Other Side</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>2</v>
+      </c>
+      <c r="C402" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist III</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>3</v>
+      </c>
+      <c r="C403" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist (2015)</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>4</v>
+      </c>
+      <c r="C404" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn (2003)</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>1</v>
+      </c>
+      <c r="C405" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 2: Dead End</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>2</v>
+      </c>
+      <c r="C406" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 3: Left for Dead</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>3</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 4: Bloody Beginnings</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>4</v>
+      </c>
+      <c r="C408" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn (2021)</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>5</v>
+      </c>
+      <c r="C409" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>1</v>
+      </c>
+      <c r="C410" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel: Part II</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>2</v>
+      </c>
+      <c r="C411" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel: Part III</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>3</v>
+      </c>
+      <c r="C412" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>1</v>
+      </c>
+      <c r="C413" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place Part II</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>2</v>
+      </c>
+      <c r="C414" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place: Day One</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>3</v>
+      </c>
+      <c r="C415" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Days Later</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>1</v>
+      </c>
+      <c r="C416" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Weeks Later</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>2</v>
+      </c>
+      <c r="C417" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Years Later</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>3</v>
+      </c>
+      <c r="C418" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Years Later: The Bone Temple</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>4</v>
+      </c>
+      <c r="C419" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>1</v>
+      </c>
+      <c r="C420" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier 2</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>2</v>
+      </c>
+      <c r="C421" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier 3</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>3</v>
+      </c>
+      <c r="C422" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3697,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B223"/>
+  <dimension ref="A1:B422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -5919,7 +8506,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>The Purge | The Purge: Season 1</t>
+          <t>The Purge | The Forever Purge</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5929,11 +8516,2001 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>The Purge | The Forever Purge</t>
+          <t>Jurassic Park (franchise) | Jurassic Park</t>
         </is>
       </c>
       <c r="B223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | The Lost World: Jurassic Park</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic Park III</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World: Fallen Kingdom</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World Dominion</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World Rebirth</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Battle of the Smithsonian</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Secret of the Tomb</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Kahmunrah Rises Again</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Dr. No</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>List of James Bond films | From Russia with Love</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Goldfinger</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Thunderball</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>List of James Bond films | You Only Live Twice</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>List of James Bond films | On Her Majesty's Secret Service</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Diamonds Are Forever</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Live and Let Die</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>List of James Bond films | The Man with the Golden Gun</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>List of James Bond films | The Spy Who Loved Me</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 2: Their First Assignment</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 3: Back in Training</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 4: Citizens on Patrol</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 5: Assignment Miami Beach</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 6: City Under Siege</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy: Mission to Moscow</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 2</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 3</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 4</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop II</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop III</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop: Axel F</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future Part II</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future Part III</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid (1984)</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid Part II</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid Part III</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Next Karate Kid</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid (2010)</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | Karate Kid: Legends</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone 2: Lost in New York</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone 3</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Sweet Home Alone</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws 2</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws 3-D</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws: The Revenge</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play (1988)</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play 2</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play 3</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Bride of Chucky</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Seed of Chucky</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Curse of Chucky</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Cult of Chucky</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play (2019)</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Evolution</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Rise of the Lycans</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Awakening</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Blood Wars</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade II</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade: Trinity</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon (2010)</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon 2</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon: The Hidden World</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon (2025)</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania 2</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania 3: Summer Vacation</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania: Transformania</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Fellowship of the Ring</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Two Towers</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Return of the King</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Finding Nemo (franchise) | Finding Nemo</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Finding Nemo (franchise) | Finding Dory</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>The Incredibles (franchise) | The Incredibles</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>The Incredibles (franchise) | Incredibles 2</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Monsters, Inc. (franchise) | Monsters, Inc.</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Monsters, Inc. (franchise) | Monsters University</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Frozen (franchise) | Frozen</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Frozen (franchise) | Frozen 2</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>National Treasure (franchise) | National Treasure</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>National Treasure (franchise) | National Treasure: Book of Secrets</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect 2</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect 3</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys II</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys for Life</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys: Ride or Die</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour 2</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour 3</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Pie</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Pie 2</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Wedding</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Reunion</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie (2000)</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 2</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 3</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 4</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 5</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie (2026)</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables 2</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables 3</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | Expend4bles</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken (2008)</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken 2 (2012)</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken 3 (2014)</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | Kingsman: The Secret Service</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | Kingsman: The Golden Circle</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | The King's Man</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me 2</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me: Now You Don't</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Zombieland (film series) | Zombieland</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Zombieland (film series) | Zombieland: Double Tap</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy Returns</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy: Tomb of the Dragon Emperor</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Zathura: A Space Adventure</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji: Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji: The Next Level</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Top Gun (franchise) | Top Gun</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Top Gun (franchise) | Top Gun: Maverick</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar: The Way of Water</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar: Fire and Ash</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron: Legacy</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron: Ares</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Legally Blonde (franchise) | Legally Blonde (2001)</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Legally Blonde (franchise) | Legally Blonde 2: Red, White &amp; Blonde (2003)</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause 2</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause 3: The Escape Clause</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clauses</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog 2</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog 3</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Movie</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Batman Movie</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Ninjago Movie</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Movie 2: The Second Part</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls World Tour</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls Band Together</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop 2</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop 3</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species II</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species III</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers 2</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers 3</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers: Reborn</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Exorcist II: The Heretic</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist III</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Exorcist: The Beginning</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Dominion: Prequel to the Exorcist</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist: Believer</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Omen (1976)</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | Damien – Omen II</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Final Conflict</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | Omen IV: The Awakening</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Omen (2006)</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The First Omen</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist (1982)</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist II: The Other Side</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist III</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist (2015)</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn (2003)</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 2: Dead End</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 3: Left for Dead</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 4: Bloody Beginnings</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn (2021)</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel: Part II</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel: Part III</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place Part II</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place: Day One</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Days Later</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Weeks Later</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Years Later</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Years Later: The Bone Temple</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier 2</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier 3</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5947,7 +10524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B223"/>
+  <dimension ref="A1:B422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -8169,21 +12746,2011 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>The Purge | The Purge: Season 1</t>
+          <t>The Purge | The Forever Purge</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>The Purge | The Forever Purge</t>
+          <t>Jurassic Park (franchise) | Jurassic Park</t>
         </is>
       </c>
       <c r="B223" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | The Lost World: Jurassic Park</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic Park III</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World: Fallen Kingdom</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World Dominion</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Jurassic Park (franchise) | Jurassic World Rebirth</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Battle of the Smithsonian</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Secret of the Tomb</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Night at the Museum (film series) | Night at the Museum: Kahmunrah Rises Again</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Dr. No</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>List of James Bond films | From Russia with Love</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Goldfinger</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Thunderball</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>List of James Bond films | You Only Live Twice</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>List of James Bond films | On Her Majesty's Secret Service</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Diamonds Are Forever</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>List of James Bond films | Live and Let Die</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>List of James Bond films | The Man with the Golden Gun</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>List of James Bond films | The Spy Who Loved Me</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 2: Their First Assignment</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 3: Back in Training</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 4: Citizens on Patrol</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 5: Assignment Miami Beach</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy 6: City Under Siege</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Police Academy (franchise) | Police Academy: Mission to Moscow</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 2</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 3</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Lethal Weapon (franchise) | Lethal Weapon 4</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop II</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
         <v>48</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop III</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Beverly Hills Cop (franchise) | Beverly Hills Cop: Axel F</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future Part II</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Back to the Future (franchise) | Back to the Future Part III</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid (1984)</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid Part II</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid Part III</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Next Karate Kid</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | The Karate Kid (2010)</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>The Karate Kid (franchise) | Karate Kid: Legends</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone 2: Lost in New York</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Alone 3</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Home Alone (franchise) | Home Sweet Home Alone</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws 2</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws 3-D</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Jaws (franchise) | Jaws: The Revenge</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play (1988)</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play 2</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play 3</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Bride of Chucky</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Seed of Chucky</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Curse of Chucky</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Cult of Chucky</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Child's Play (franchise) | Child's Play (2019)</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Evolution</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Rise of the Lycans</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Awakening</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Underworld (film series) | Underworld: Blood Wars</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade II</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Blade (franchise) | Blade: Trinity</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon (2010)</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon 2</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon: The Hidden World</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>How to Train Your Dragon (franchise) | How to Train Your Dragon (2025)</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania 2</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania 3: Summer Vacation</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Hotel Transylvania (franchise) | Hotel Transylvania: Transformania</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Fellowship of the Ring</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Two Towers</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings (film series) | The Return of the King</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Finding Nemo (franchise) | Finding Nemo</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Finding Nemo (franchise) | Finding Dory</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>The Incredibles (franchise) | The Incredibles</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>The Incredibles (franchise) | Incredibles 2</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Monsters, Inc. (franchise) | Monsters, Inc.</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Monsters, Inc. (franchise) | Monsters University</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Frozen (franchise) | Frozen</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Frozen (franchise) | Frozen 2</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>National Treasure (franchise) | National Treasure</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>National Treasure (franchise) | National Treasure: Book of Secrets</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect 2</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Pitch Perfect (film series) | Pitch Perfect 3</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys II</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys for Life</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Bad Boys (franchise) | Bad Boys: Ride or Die</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour 2</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Rush Hour (franchise) | Rush Hour 3</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Pie</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Pie 2</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Wedding</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>American Pie (film series) | American Reunion</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie (2000)</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 2</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 3</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 4</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie 5</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Scary Movie (film series) | Scary Movie (2026)</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables 2</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | The Expendables 3</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>The Expendables (franchise) | Expend4bles</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken (2008)</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken 2 (2012)</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Taken (franchise) | Taken 3 (2014)</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | Kingsman: The Secret Service</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | Kingsman: The Golden Circle</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Kingsman (franchise) | The King's Man</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me 2</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Now You See Me (film series) | Now You See Me: Now You Don't</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Zombieland (film series) | Zombieland</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Zombieland (film series) | Zombieland: Double Tap</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy Returns</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>The Mummy (franchise) | The Mummy: Tomb of the Dragon Emperor</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Zathura: A Space Adventure</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji: Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Jumanji (franchise) | Jumanji: The Next Level</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Top Gun (franchise) | Top Gun</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Top Gun (franchise) | Top Gun: Maverick</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar: The Way of Water</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Avatar (franchise) | Avatar: Fire and Ash</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron: Legacy</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Tron (franchise) | Tron: Ares</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Legally Blonde (franchise) | Legally Blonde (2001)</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Legally Blonde (franchise) | Legally Blonde 2: Red, White &amp; Blonde (2003)</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause 2</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clause 3: The Escape Clause</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>The Santa Clause (franchise) | The Santa Clauses</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog 2</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog (film series) | Sonic the Hedgehog 3</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Movie</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Batman Movie</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Ninjago Movie</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>The Lego Movie (franchise) | The Lego Movie 2: The Second Part</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls World Tour</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Trolls (franchise) | Trolls Band Together</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop 2</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Robocop (franchise) | RoboCop 3</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species II</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Species (film series) | Species III</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers 2</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers 3</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Jeepers Creepers (film series) | Jeepers Creepers: Reborn</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Exorcist II: The Heretic</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist III</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Exorcist: The Beginning</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | Dominion: Prequel to the Exorcist</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>The Exorcist (franchise) | The Exorcist: Believer</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Omen (1976)</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | Damien – Omen II</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Final Conflict</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | Omen IV: The Awakening</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The Omen (2006)</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>The Omen (franchise) | The First Omen</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist (1982)</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist II: The Other Side</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist III</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Poltergeist (franchise) | Poltergeist (2015)</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn (2003)</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 2: Dead End</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 3: Left for Dead</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn 4: Bloody Beginnings</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Wrong Turn (film series) | Wrong Turn (2021)</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel: Part II</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Hostel (film series) | Hostel: Part III</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place Part II</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>A Quiet Place (franchise) | A Quiet Place: Day One</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Days Later</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Weeks Later</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Years Later</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>28 Days Later (franchise) | 28 Years Later: The Bone Temple</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier 2</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Terrifier (film series) | Terrifier 3</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -8201,8 +14768,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -8245,14 +14812,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.89296, 66.1264</t>
+          <t>-2.18255, 64.3415</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.031</v>
+        <v>0.0322</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0266</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="3">
@@ -8266,14 +14833,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.502897, -6.62146, 74.2702</t>
+          <t>0.955657, -10.6644, 77.7419</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0459</v>
+        <v>0.0741</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0372</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="4">
@@ -8287,14 +14854,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.349487, 5.75235, -28.3681, 96.5807</t>
+          <t>-0.334348, 5.80814, -29.8174, 96.4572</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="5">
@@ -8308,14 +14875,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0142773, -0.644388, 7.76554, -33.4995, 100.363</t>
+          <t>0.0118707, -0.57392, 7.39343, -33.7036, 99.2239</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1051</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0716</v>
+        <v>0.0965</v>
       </c>
     </row>
     <row r="6">
@@ -8332,7 +14899,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222</v>
+        <v>421</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -8345,7 +14912,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1762</v>
+        <v>-0.1795</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -8358,7 +14925,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008522252747016413</v>
+        <v>0.0002134620872604367</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -8387,7 +14954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>y = -1.89x + 66.1</t>
+          <t>y = -2.18x + 64.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>

--- a/002/xy_002_data.xlsx
+++ b/002/xy_002_data.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26/09/2026 19:36</t>
+          <t>26/09/2026 20:19</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rotten Tomatoes Tomatometer, % of critics positive, as listed on each film's Wikipedia franchise page, pulled 26/09/2026</t>
+          <t>Rotten Tomatoes Tomatometer, % of critics positive, with review counts, as listed on each film's Wikipedia franchise page, pulled 26/09/2026</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26/09/2026 19:36</t>
+          <t>26/09/2026 20:19</t>
         </is>
       </c>
     </row>
@@ -755,10 +755,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>robustness</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Robustness: adjusting each score for its number of critic reviews (empirical Bayes) moves every median by 1 point or less, and 66 of 87 first sequels still score below their original. Boxes with fewer than 10 films are faded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>correlation is not causation</t>
         </is>
